--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -413,8 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
+    <col hidden="1" width="13" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="13" customWidth="1" min="6" max="6"/>
+    <col hidden="1" width="13" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -429,22 +436,32 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>registered_at_utc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>participant_no</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>entered_name</t>
+          <t>referrer_user_id</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>registered_at_utc</t>
+          <t>invites_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entries_count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>referral_qualified</t>
         </is>
       </c>
     </row>
@@ -459,23 +476,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>𝙂𝙊𝘿𝙕𝙊 𝙍𝙀𝙎𝙀𝙇𝙇𝙀𝙍</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+998507040800</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sardor Qudratov</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>2026-02-27T12:36:30+00:00</t>
         </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -489,23 +500,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ilhom</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>998904543968</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aralov Ilhom</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>2026-02-27T12:40:50+00:00</t>
         </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -519,23 +524,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SARDOR </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+998882314020</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sardor Qudratov</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>2026-02-27T12:50:10+00:00</t>
         </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -549,23 +548,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>❖Ƭʜᴇ 𝙓𝙊'𝙅𝘼𝙔𝙊𝙍𝙊𝙑 𝙿𝙼</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>998902838083</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Asilbek</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>2026-02-27T13:07:52+00:00</t>
         </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -579,23 +572,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bahromjon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>998994676977</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Bahromjon</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>2026-02-27T14:08:58+00:00</t>
         </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -609,23 +596,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JONY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>79141659518</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>JAXONGIR YQXSHIBOYEV</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>2026-02-27T15:29:45+00:00</t>
         </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5483588647</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Godzo_Zavachi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-02-28T11:38:15+00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
